--- a/artfynd/A 18975-2019 artfynd.xlsx
+++ b/artfynd/A 18975-2019 artfynd.xlsx
@@ -795,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113162257</v>
+        <v>113162263</v>
       </c>
       <c r="B3" t="n">
-        <v>57379</v>
+        <v>56891</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,25 +807,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103042</v>
+        <v>103035</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Kråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Corvus corone</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -837,7 +837,7 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -847,10 +847,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>334232</v>
+        <v>334288</v>
       </c>
       <c r="R3" t="n">
-        <v>6396917</v>
+        <v>6396919</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -909,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113162197</v>
+        <v>113162257</v>
       </c>
       <c r="B4" t="n">
-        <v>57149</v>
+        <v>57379</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -921,25 +921,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103037</v>
+        <v>103042</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stare</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sturnus vulgaris</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -951,7 +951,7 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>besöker bebott bo</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -961,10 +961,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>334272</v>
+        <v>334232</v>
       </c>
       <c r="R4" t="n">
-        <v>6396867</v>
+        <v>6396917</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -991,12 +991,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-06-01</t>
+          <t>2022-05-06</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-06-01</t>
+          <t>2022-05-06</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,10 +1023,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113162263</v>
+        <v>113162197</v>
       </c>
       <c r="B5" t="n">
-        <v>56891</v>
+        <v>57149</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1035,20 +1035,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103035</v>
+        <v>103037</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kråka</t>
+          <t>Stare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Corvus corone</t>
+          <t>Sturnus vulgaris</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1065,7 +1065,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>besöker bebott bo</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1075,10 +1075,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>334288</v>
+        <v>334272</v>
       </c>
       <c r="R5" t="n">
-        <v>6396919</v>
+        <v>6396867</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1105,12 +1105,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-05-06</t>
+          <t>2022-06-01</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-05-06</t>
+          <t>2022-06-01</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 18975-2019 artfynd.xlsx
+++ b/artfynd/A 18975-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113124715</v>
       </c>
       <c r="B2" t="n">
-        <v>57949</v>
+        <v>57950</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113162263</v>
+        <v>113162257</v>
       </c>
       <c r="B3" t="n">
-        <v>56891</v>
+        <v>57380</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,25 +807,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103035</v>
+        <v>103042</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kråka</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Corvus corone</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -837,7 +837,7 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -847,10 +847,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>334288</v>
+        <v>334232</v>
       </c>
       <c r="R3" t="n">
-        <v>6396919</v>
+        <v>6396917</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -909,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113162257</v>
+        <v>113162263</v>
       </c>
       <c r="B4" t="n">
-        <v>57379</v>
+        <v>56892</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -921,25 +921,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103042</v>
+        <v>103035</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Kråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Corvus corone</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -951,7 +951,7 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -961,10 +961,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>334232</v>
+        <v>334288</v>
       </c>
       <c r="R4" t="n">
-        <v>6396917</v>
+        <v>6396919</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -1026,7 +1026,7 @@
         <v>113162197</v>
       </c>
       <c r="B5" t="n">
-        <v>57149</v>
+        <v>57150</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 18975-2019 artfynd.xlsx
+++ b/artfynd/A 18975-2019 artfynd.xlsx
@@ -909,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113162263</v>
+        <v>113162197</v>
       </c>
       <c r="B4" t="n">
-        <v>56892</v>
+        <v>57150</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -921,20 +921,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103035</v>
+        <v>103037</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kråka</t>
+          <t>Stare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Corvus corone</t>
+          <t>Sturnus vulgaris</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -951,7 +951,7 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>besöker bebott bo</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -961,10 +961,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>334288</v>
+        <v>334272</v>
       </c>
       <c r="R4" t="n">
-        <v>6396919</v>
+        <v>6396867</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -991,12 +991,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-05-06</t>
+          <t>2022-06-01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-05-06</t>
+          <t>2022-06-01</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,10 +1023,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113162197</v>
+        <v>113162263</v>
       </c>
       <c r="B5" t="n">
-        <v>57150</v>
+        <v>56892</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1035,20 +1035,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103037</v>
+        <v>103035</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stare</t>
+          <t>Kråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sturnus vulgaris</t>
+          <t>Corvus corone</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1065,7 +1065,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>besöker bebott bo</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1075,10 +1075,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>334272</v>
+        <v>334288</v>
       </c>
       <c r="R5" t="n">
-        <v>6396867</v>
+        <v>6396919</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1105,12 +1105,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-06-01</t>
+          <t>2022-05-06</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-06-01</t>
+          <t>2022-05-06</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 18975-2019 artfynd.xlsx
+++ b/artfynd/A 18975-2019 artfynd.xlsx
@@ -795,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113162257</v>
+        <v>113162197</v>
       </c>
       <c r="B3" t="n">
-        <v>57380</v>
+        <v>57150</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,25 +807,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103042</v>
+        <v>103037</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Stare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Sturnus vulgaris</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -837,7 +837,7 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>besöker bebott bo</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -847,10 +847,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>334232</v>
+        <v>334272</v>
       </c>
       <c r="R3" t="n">
-        <v>6396917</v>
+        <v>6396867</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -877,12 +877,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-05-06</t>
+          <t>2022-06-01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-05-06</t>
+          <t>2022-06-01</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113162197</v>
+        <v>113162263</v>
       </c>
       <c r="B4" t="n">
-        <v>57150</v>
+        <v>56892</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -921,20 +921,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103037</v>
+        <v>103035</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stare</t>
+          <t>Kråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sturnus vulgaris</t>
+          <t>Corvus corone</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -951,7 +951,7 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>besöker bebott bo</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -961,10 +961,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>334272</v>
+        <v>334288</v>
       </c>
       <c r="R4" t="n">
-        <v>6396867</v>
+        <v>6396919</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -991,12 +991,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-06-01</t>
+          <t>2022-05-06</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-06-01</t>
+          <t>2022-05-06</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,10 +1023,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113162263</v>
+        <v>113162257</v>
       </c>
       <c r="B5" t="n">
-        <v>56892</v>
+        <v>57380</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1035,25 +1035,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103035</v>
+        <v>103042</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kråka</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Corvus corone</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1065,7 +1065,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1075,10 +1075,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>334288</v>
+        <v>334232</v>
       </c>
       <c r="R5" t="n">
-        <v>6396919</v>
+        <v>6396917</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>

--- a/artfynd/A 18975-2019 artfynd.xlsx
+++ b/artfynd/A 18975-2019 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>113162197</v>
       </c>
       <c r="B3" t="n">
-        <v>57150</v>
+        <v>57153</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>113162263</v>
       </c>
       <c r="B4" t="n">
-        <v>56892</v>
+        <v>56895</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>113162257</v>
       </c>
       <c r="B5" t="n">
-        <v>57380</v>
+        <v>57383</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 18975-2019 artfynd.xlsx
+++ b/artfynd/A 18975-2019 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
